--- a/docs/test-data/tire-import/05-numeric-serials.xlsx
+++ b/docs/test-data/tire-import/05-numeric-serials.xlsx
@@ -41,24 +41,6 @@
   </si>
   <si>
     <t>ซีรีย์ตัวเลขล้วน</t>
-  </si>
-  <si>
-    <t>GOODYEAR</t>
-  </si>
-  <si>
-    <t>KMAX S</t>
-  </si>
-  <si>
-    <t>295/80R22.5</t>
-  </si>
-  <si>
-    <t>HANKOOK</t>
-  </si>
-  <si>
-    <t>AH35</t>
-  </si>
-  <si>
-    <t>315/80R22.5</t>
   </si>
 </sst>
 </file>
@@ -146,7 +128,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>6642774900</v>
+        <v>7074218000</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -154,16 +136,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>6642774901</v>
+        <v>7074218001</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -171,16 +153,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>6642774902</v>
+        <v>7074218002</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -197,7 +179,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>6642774903</v>
+        <v>7074218003</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -205,16 +187,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>6642774904</v>
+        <v>7074218004</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
